--- a/backend/static/posters/ASK_Recipes_v1.2.xlsx
+++ b/backend/static/posters/ASK_Recipes_v1.2.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Image Path</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
@@ -15805,7 +15805,7 @@
       <c r="AD82" s="2" t="inlineStr"/>
       <c r="AE82" s="2" t="inlineStr">
         <is>
-          <t>images/Shourba_Ades.jpg</t>
+          <t>Shourba_Ades.jpg</t>
         </is>
       </c>
       <c r="AF82" s="2" t="inlineStr"/>
